--- a/www/download/IND.labour_force_value.s.mv.rpA1.xlsx
+++ b/www/download/IND.labour_force_value.s.mv.rpA1.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>7706.776</t>
+          <t>7706776296.97865</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8026.122</t>
+          <t>8026121806.69672</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>7822.12</t>
+          <t>7822119864.33946</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8090.626</t>
+          <t>8090625833.53655</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8722.09</t>
+          <t>8722090301.5301</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8520.243</t>
+          <t>8520243203.86394</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8294.26</t>
+          <t>8294259736.89604</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8866.513</t>
+          <t>8866512540.90696</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>9634.378</t>
+          <t>9634378162.43835</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>11420.688</t>
+          <t>11420688109.0368</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12355.825</t>
+          <t>12355825384.9922</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>12302.128</t>
+          <t>12302128465.683</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>12841.513</t>
+          <t>12841512835.9654</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>12577.568</t>
+          <t>12577568113.9243</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>12692.99</t>
+          <t>12692989872.5221</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4672.373</t>
+          <t>4672372552.43287</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4508.849</t>
+          <t>4508848994.91201</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3890.283</t>
+          <t>3890283158.12024</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4006.234</t>
+          <t>4006233954.10806</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4102.715</t>
+          <t>4102714784.39689</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3960.6</t>
+          <t>3960599666.92198</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4038.075</t>
+          <t>4038075024.81331</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4042.248</t>
+          <t>4042248362.97039</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4416.84</t>
+          <t>4416839914.81382</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4628.32</t>
+          <t>4628319816.35109</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>4702.023</t>
+          <t>4702023268.30214</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4818.522</t>
+          <t>4818522416.14766</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>4872.564</t>
+          <t>4872564425.9953</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>4775.814</t>
+          <t>4775814139.69682</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>4334.862</t>
+          <t>4334861755.0568</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5790.402</t>
+          <t>5790401683.85665</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5902.218</t>
+          <t>5902218075.18032</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5705.56</t>
+          <t>5705560162.34709</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5775.108</t>
+          <t>5775107995.98699</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6436.424</t>
+          <t>6436424358.41716</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6791.497</t>
+          <t>6791497395.04243</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7302.144</t>
+          <t>7302144037.74435</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>7876.621</t>
+          <t>7876620763.28485</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>9603.645</t>
+          <t>9603645104.59841</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>10185.642</t>
+          <t>10185642355.0803</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10107.921</t>
+          <t>10107921052.8168</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>10087.969</t>
+          <t>10087969357.8067</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>9732.892</t>
+          <t>9732891533.50633</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>8881.205</t>
+          <t>8881205490.47358</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>9184.12</t>
+          <t>9184119753.46101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1317.181</t>
+          <t>1317180882.18169</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1184.698</t>
+          <t>1184698059.04804</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>996.602</t>
+          <t>996601649.615024</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1172.587</t>
+          <t>1172587424.95294</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1015.843</t>
+          <t>1015842860.33627</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>928.713</t>
+          <t>928712678.283533</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>942.196</t>
+          <t>942195741.930458</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>903.175</t>
+          <t>903175468.909723</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>929.798</t>
+          <t>929797670.422139</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>937.329</t>
+          <t>937328918.705559</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>931.606</t>
+          <t>931606326.030477</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>932.796</t>
+          <t>932796154.587397</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>999.208</t>
+          <t>999208117.342058</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1091.138</t>
+          <t>1091137683.93195</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>1174.138</t>
+          <t>1174138378.26948</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>41422.505</t>
+          <t>41422505148.8963</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>40133.482</t>
+          <t>40133481932.6011</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38569.118</t>
+          <t>38569118448.3573</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>38632.391</t>
+          <t>38632390531.7062</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>36269.792</t>
+          <t>36269792280.7639</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>36375.488</t>
+          <t>36375487780.6685</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35202.348</t>
+          <t>35202348187.3429</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35234.51</t>
+          <t>35234510278.8817</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>35068.35</t>
+          <t>35068350251.9891</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>37102.962</t>
+          <t>37102962227.7807</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>39639.099</t>
+          <t>39639099253.867</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>40868.156</t>
+          <t>40868155653.8324</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>41695.254</t>
+          <t>41695254096.5865</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>43770.875</t>
+          <t>43770874812.099</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>44096.863</t>
+          <t>44096862985.9034</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11808.17</t>
+          <t>11808169936.3875</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11447.437</t>
+          <t>11447437005.6584</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10901.57</t>
+          <t>10901569564.8184</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11823.388</t>
+          <t>11823388374.1679</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>12734.26</t>
+          <t>12734260275.2888</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>14211.838</t>
+          <t>14211837808.2041</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>15253.532</t>
+          <t>15253531528.5299</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>15470.381</t>
+          <t>15470380792.3495</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>16742.965</t>
+          <t>16742965253.5372</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>17806.574</t>
+          <t>17806574066.5473</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>19352.261</t>
+          <t>19352261424.3043</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>20405.895</t>
+          <t>20405895272.3339</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>19866.892</t>
+          <t>19866891865.2136</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>19756.59</t>
+          <t>19756590384.7102</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>17583.35</t>
+          <t>17583349757.7475</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>596946.554</t>
+          <t>596946553672.313</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>589384.384</t>
+          <t>589384383508.25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>588155.812</t>
+          <t>588155811691.746</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>573910.41</t>
+          <t>573910410175.262</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>554733.979</t>
+          <t>554733979100.425</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>538289.059</t>
+          <t>538289059288.304</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>534277.285</t>
+          <t>534277284659.398</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>534591.93</t>
+          <t>534591929631.442</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>524814.726</t>
+          <t>524814726449.5</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>517399.98</t>
+          <t>517399979582.325</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>502177.166</t>
+          <t>502177166156.866</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>490227.056</t>
+          <t>490227056152.32</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>457334.038</t>
+          <t>457334037702.115</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>473774.183</t>
+          <t>473774183203.498</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>473622.407</t>
+          <t>473622406870.015</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>205.528</t>
+          <t>205527859.985308</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>213.651</t>
+          <t>213650981.420658</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>186.961</t>
+          <t>186960715.634142</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>197.477</t>
+          <t>197477311.989313</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>220.902</t>
+          <t>220902463.625141</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>220.557</t>
+          <t>220556839.715532</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>247.081</t>
+          <t>247080752.523581</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>257.565</t>
+          <t>257565223.30467</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>298.665</t>
+          <t>298664530.792763</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>289.618</t>
+          <t>289618072.779985</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>291.56</t>
+          <t>291559892.281896</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>299.284</t>
+          <t>299283558.400031</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>281.671</t>
+          <t>281670878.867592</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>342.224</t>
+          <t>342223830.265694</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>279.728</t>
+          <t>279727786.843144</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1872.402</t>
+          <t>1872401683.55264</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2675.494</t>
+          <t>2675493594.70606</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2469.505</t>
+          <t>2469505371.57903</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2447.534</t>
+          <t>2447533605.54659</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2374.425</t>
+          <t>2374424995.25339</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2269.636</t>
+          <t>2269635631.91859</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2381.157</t>
+          <t>2381157431.84919</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2437.213</t>
+          <t>2437213351.66704</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2609.165</t>
+          <t>2609164914.30209</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2841.202</t>
+          <t>2841202289.15179</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>3015.943</t>
+          <t>3015943308.62862</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2958.965</t>
+          <t>2958965294.40149</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>3085.173</t>
+          <t>3085172644.89264</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3065.701</t>
+          <t>3065700892.71617</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2626.62</t>
+          <t>2626619873.78727</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>54873.719</t>
+          <t>54873718838.8299</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>49037.764</t>
+          <t>49037763638.6798</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42615.308</t>
+          <t>42615308329.3021</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>44273.557</t>
+          <t>44273556685.7135</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45732.076</t>
+          <t>45732075852.9457</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>48108.871</t>
+          <t>48108870612.6511</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>46763.805</t>
+          <t>46763804944.844</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>46252.327</t>
+          <t>46252327459.6542</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>52318.951</t>
+          <t>52318951472.4517</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>53100.679</t>
+          <t>53100679113.1718</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>50342.553</t>
+          <t>50342553080.542</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>50583.825</t>
+          <t>50583825300.3536</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>52303.01</t>
+          <t>52303010240.5859</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>49903.449</t>
+          <t>49903449024.429</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>46643.595</t>
+          <t>46643595364.2622</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4160.407</t>
+          <t>4160406897.04497</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4081.915</t>
+          <t>4081914992.63294</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3213.837</t>
+          <t>3213837196.50564</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3599.513</t>
+          <t>3599513452.6775</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3695.606</t>
+          <t>3695605527.76554</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3559.517</t>
+          <t>3559516642.71198</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3764.406</t>
+          <t>3764406270.09022</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3878.948</t>
+          <t>3878947745.27709</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4407.181</t>
+          <t>4407180859.77164</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4426.1</t>
+          <t>4426100434.84885</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>4475.854</t>
+          <t>4475854364.91717</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4608.817</t>
+          <t>4608817457.19112</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>4670.344</t>
+          <t>4670344476.56429</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>4450.549</t>
+          <t>4450549439.84112</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3841.368</t>
+          <t>3841367653.63905</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11814.983</t>
+          <t>11814982923.8939</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11542.638</t>
+          <t>11542637574.6388</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10274.243</t>
+          <t>10274243459.343</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11738.279</t>
+          <t>11738278633.8372</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13090.306</t>
+          <t>13090305532.6378</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>13593.35</t>
+          <t>13593350406.9576</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>14861.48</t>
+          <t>14861479748.6861</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>15956.629</t>
+          <t>15956629194.3801</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18081.25</t>
+          <t>18081249745.8983</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>19315.097</t>
+          <t>19315097297.2249</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>20213.817</t>
+          <t>20213816950.1751</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>21296.156</t>
+          <t>21296155674.5506</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>21567.845</t>
+          <t>21567845412.5051</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>21111.595</t>
+          <t>21111595417.7292</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>17830.989</t>
+          <t>17830989093.3835</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>274.853</t>
+          <t>274852529.269854</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>288.486</t>
+          <t>288485998.32636</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>297.446</t>
+          <t>297445680.219764</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>309.941</t>
+          <t>309940652.958745</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>289.357</t>
+          <t>289356956.449582</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>330.65</t>
+          <t>330650006.002039</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>341.704</t>
+          <t>341704201.797936</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>429.922</t>
+          <t>429922331.414721</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>510.098</t>
+          <t>510098147.524135</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>523.693</t>
+          <t>523693140.117104</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>507.615</t>
+          <t>507615341.065859</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>522.81</t>
+          <t>522810493.678008</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>542.877</t>
+          <t>542876775.430725</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>591.877</t>
+          <t>591876600.21978</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>478.176</t>
+          <t>478176342.766882</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2225.829</t>
+          <t>2225828861.63571</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2297.254</t>
+          <t>2297253985.87467</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1992.343</t>
+          <t>1992342884.12835</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2173.669</t>
+          <t>2173668779.53822</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2240.832</t>
+          <t>2240831509.4752</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2065.374</t>
+          <t>2065374492.33667</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2156.952</t>
+          <t>2156951635.90644</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2205.324</t>
+          <t>2205324058.02163</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2460.168</t>
+          <t>2460168082.02869</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2592.97</t>
+          <t>2592969978.84907</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2676.937</t>
+          <t>2676936573.19358</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2810.379</t>
+          <t>2810379017.35258</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2860.781</t>
+          <t>2860781192.74195</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2833.959</t>
+          <t>2833959161.18656</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2540.982</t>
+          <t>2540982304.34147</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>25801.795</t>
+          <t>25801795024.2439</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25961.766</t>
+          <t>25961765837.3114</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>22469.124</t>
+          <t>22469124171.9283</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25209.081</t>
+          <t>25209081227.0103</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>27502.757</t>
+          <t>27502757214.6828</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>27772.74</t>
+          <t>27772739983.1705</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>29706.683</t>
+          <t>29706683022.5894</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>30680.421</t>
+          <t>30680420803.4803</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>33375.745</t>
+          <t>33375744691.8368</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>34647.628</t>
+          <t>34647627739.3201</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>34970.008</t>
+          <t>34970007691.292</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>34125.151</t>
+          <t>34125151169.8862</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>34304.544</t>
+          <t>34304544292.076</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>33340.038</t>
+          <t>33340037894.9595</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>30444.903</t>
+          <t>30444902554.9078</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>24844.822</t>
+          <t>24844822359.1862</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>25390.317</t>
+          <t>25390316929.4104</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>24168.938</t>
+          <t>24168938273.0434</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>26636.347</t>
+          <t>26636347193.6008</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>28499.62</t>
+          <t>28499619687.5497</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>30030.276</t>
+          <t>30030276391.2855</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>31838.308</t>
+          <t>31838307951.5624</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>32739.649</t>
+          <t>32739648941.3794</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>34767.348</t>
+          <t>34767348397.1197</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>37058.359</t>
+          <t>37058358727.1629</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>37411.613</t>
+          <t>37411613245.9666</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>37742.011</t>
+          <t>37742010519.3155</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>36934.586</t>
+          <t>36934585523.1985</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>32580.085</t>
+          <t>32580084915.3113</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>29297.368</t>
+          <t>29297367843.3983</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2070.434</t>
+          <t>2070434029.96974</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2141.661</t>
+          <t>2141660867.35594</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2041.25</t>
+          <t>2041249858.33006</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2105.44</t>
+          <t>2105440028.90494</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2282.289</t>
+          <t>2282289258.54912</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2426.24</t>
+          <t>2426240097.25613</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2354.776</t>
+          <t>2354775813.15996</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2780.939</t>
+          <t>2780938664.2284</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2877.402</t>
+          <t>2877402372.49955</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2964.81</t>
+          <t>2964810310.79587</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2906.432</t>
+          <t>2906432174.52813</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3148.041</t>
+          <t>3148040619.319</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3356.986</t>
+          <t>3356986112.49573</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>3408.651</t>
+          <t>3408651318.57335</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>3294.976</t>
+          <t>3294975569.56148</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2546.031</t>
+          <t>2546031313.0416</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2399.088</t>
+          <t>2399087903.09915</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2269.038</t>
+          <t>2269037686.88141</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2289.597</t>
+          <t>2289596878.4371</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2423.322</t>
+          <t>2423322030.1327</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2415.081</t>
+          <t>2415080880.7437</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2360.389</t>
+          <t>2360388752.3534</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2568.312</t>
+          <t>2568312259.45115</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2761.227</t>
+          <t>2761227178.51057</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2377.565</t>
+          <t>2377565482.46383</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2366.248</t>
+          <t>2366247729.27972</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2265.145</t>
+          <t>2265144732.75812</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2348.058</t>
+          <t>2348057854.2531</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2146.273</t>
+          <t>2146272758.17045</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1918.427</t>
+          <t>1918426567.11408</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>25158.044</t>
+          <t>25158044059.7051</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25499.06</t>
+          <t>25499059652.6596</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22957.016</t>
+          <t>22957016398.6178</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>21833.5</t>
+          <t>21833500353.8602</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>24213.579</t>
+          <t>24213578764.8576</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>25959.248</t>
+          <t>25959248108.8638</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>27084.571</t>
+          <t>27084571330.7367</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>28483.407</t>
+          <t>28483406774.114</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>30604.834</t>
+          <t>30604834399.8748</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>31255.713</t>
+          <t>31255712790.7079</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>29672.698</t>
+          <t>29672697619.8583</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>29671.827</t>
+          <t>29671827111.28</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>31689.842</t>
+          <t>31689841813.4956</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>31472.947</t>
+          <t>31472947492.5357</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>33742.451</t>
+          <t>33742451323.6668</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>290062.905</t>
+          <t>290062905063.841</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>272364.224</t>
+          <t>272364223881.546</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>288094.284</t>
+          <t>288094284301.698</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>285955.942</t>
+          <t>285955942014.85</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>279015.366</t>
+          <t>279015365918.564</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>281644.902</t>
+          <t>281644901799.948</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>290738.895</t>
+          <t>290738895081.937</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>277148.716</t>
+          <t>277148716186.144</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>299847.573</t>
+          <t>299847572793.339</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>314133.673</t>
+          <t>314133673022.898</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>326465.997</t>
+          <t>326465997469.843</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>330867.061</t>
+          <t>330867061406.048</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>312992.782</t>
+          <t>312992782336.328</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>305453.645</t>
+          <t>305453645334.545</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>321513.186</t>
+          <t>321513186126.364</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1235.452</t>
+          <t>1235452125.29333</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1321.241</t>
+          <t>1321241289.4898</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1205.704</t>
+          <t>1205704368.79106</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1243.342</t>
+          <t>1243342491.80117</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1312.784</t>
+          <t>1312783699.38173</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1390.447</t>
+          <t>1390447109.81224</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1591.902</t>
+          <t>1591901606.73887</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1710.152</t>
+          <t>1710151784.62965</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1569.116</t>
+          <t>1569116403.66502</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1530.49</t>
+          <t>1530490160.77999</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1803.652</t>
+          <t>1803652450.14311</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>1866.26</t>
+          <t>1866260357.83614</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2070.34</t>
+          <t>2070340163.26399</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2096.342</t>
+          <t>2096342446.79429</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2076.953</t>
+          <t>2076953369.14669</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17613.336</t>
+          <t>17613336414.6599</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>17479.367</t>
+          <t>17479367411.3321</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>16093.183</t>
+          <t>16093183182.0255</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>16390.316</t>
+          <t>16390316042.4346</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>16824.241</t>
+          <t>16824241209.9468</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>17058.989</t>
+          <t>17058988818.181</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>18132.308</t>
+          <t>18132307978.3192</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18988.218</t>
+          <t>18988218017.757</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>21156.202</t>
+          <t>21156201595.6837</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>22688.171</t>
+          <t>22688171319.8274</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>23029.478</t>
+          <t>23029478336.0932</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>23853.245</t>
+          <t>23853244755.2972</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>23054.047</t>
+          <t>23054047437.2114</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>21860.311</t>
+          <t>21860311196.6592</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>19207.654</t>
+          <t>19207654159.0955</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>82640.455</t>
+          <t>82640455440.9184</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>73505.152</t>
+          <t>73505151585.8699</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>65862.013</t>
+          <t>65862013073.189</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>62507.183</t>
+          <t>62507183157.7875</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>65353.06</t>
+          <t>65353059829.3423</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>69792.88</t>
+          <t>69792879599.0804</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>68456.94</t>
+          <t>68456939915.7623</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>64425.702</t>
+          <t>64425701837.7262</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>66258.207</t>
+          <t>66258207312.9689</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>70223.893</t>
+          <t>70223892699.8687</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>69857.034</t>
+          <t>69857033639.0989</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>67976.283</t>
+          <t>67976282956.2112</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>61742.964</t>
+          <t>61742963633.2364</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>58684.675</t>
+          <t>58684675328.9049</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>56380.388</t>
+          <t>56380387595.1596</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19870.239</t>
+          <t>19870238735.8992</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19356.813</t>
+          <t>19356813043.273</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>17753.367</t>
+          <t>17753367035.9284</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>14788.414</t>
+          <t>14788414014.8811</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>15128.465</t>
+          <t>15128464887.3635</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>16359.771</t>
+          <t>16359770609.8267</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>16615.458</t>
+          <t>16615458376.4148</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>17410.753</t>
+          <t>17410752956.2594</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>18876.923</t>
+          <t>18876922861.6771</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>20134.114</t>
+          <t>20134113553.5136</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>20262.716</t>
+          <t>20262715745.5019</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>21239.473</t>
+          <t>21239472684.0539</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>20641.072</t>
+          <t>20641072435.0305</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>19013.475</t>
+          <t>19013474581.2938</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>17967.595</t>
+          <t>17967594574.6468</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>616.521</t>
+          <t>616520947.847705</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>623.417</t>
+          <t>623417388.732472</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>617.506</t>
+          <t>617506315.168986</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>757.901</t>
+          <t>757900669.651546</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>774.543</t>
+          <t>774542798.94555</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>791.981</t>
+          <t>791981139.916194</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>751.989</t>
+          <t>751989070.268185</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>791.218</t>
+          <t>791217815.859613</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>888.081</t>
+          <t>888080666.793467</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>783.56</t>
+          <t>783559984.397012</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>857.928</t>
+          <t>857927918.642581</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>908.246</t>
+          <t>908245949.578283</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>919.675</t>
+          <t>919675365.632833</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1005.508</t>
+          <t>1005507517.14961</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>885.023</t>
+          <t>885023457.765241</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>294.067</t>
+          <t>294067238.618206</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>260.606</t>
+          <t>260606315.238303</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>227.027</t>
+          <t>227027010.086429</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>233.731</t>
+          <t>233730801.906284</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>259.836</t>
+          <t>259835990.508256</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>280.332</t>
+          <t>280332062.030603</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>269.455</t>
+          <t>269454927.816514</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>296.582</t>
+          <t>296581526.733504</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>317.085</t>
+          <t>317084946.45442</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>338.352</t>
+          <t>338351533.074349</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>363.862</t>
+          <t>363861705.499389</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>364.779</t>
+          <t>364778700.22256</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>335.11</t>
+          <t>335110214.435151</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>393.805</t>
+          <t>393804728.352382</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>339.095</t>
+          <t>339094848.287902</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>362.956</t>
+          <t>362956409.313455</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>385.258</t>
+          <t>385257931.850262</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>371.46</t>
+          <t>371460037.866316</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>395.424</t>
+          <t>395423673.880229</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>397.292</t>
+          <t>397291836.335709</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>343.18</t>
+          <t>343179876.788422</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>331.99</t>
+          <t>331990407.418274</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>324.44</t>
+          <t>324440052.669444</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>348.842</t>
+          <t>348841773.516259</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>351.746</t>
+          <t>351746156.123361</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>383.662</t>
+          <t>383661933.955552</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>429.92</t>
+          <t>429919652.815648</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>514.589</t>
+          <t>514588507.482085</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>570.572</t>
+          <t>570571936.22661</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>424.257</t>
+          <t>424256969.355627</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10884.173</t>
+          <t>10884173257.0817</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>10727.26</t>
+          <t>10727259603.8969</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10576.79</t>
+          <t>10576790200.2896</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>11706.65</t>
+          <t>11706649796.4638</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>12816.891</t>
+          <t>12816890719.4126</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>13664.063</t>
+          <t>13664063224.8121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>15420.096</t>
+          <t>15420096434.4084</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>15499.29</t>
+          <t>15499290498.0983</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>15705.562</t>
+          <t>15705561927.2371</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>15718.774</t>
+          <t>15718773865.8214</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>15607.599</t>
+          <t>15607599448.3189</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>15211.4</t>
+          <t>15211399709.1728</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>14886.815</t>
+          <t>14886815441.7072</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>15552.083</t>
+          <t>15552082957.7176</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>15251.545</t>
+          <t>15251544783.5566</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>99.104</t>
+          <t>99104159.4571918</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>106.148</t>
+          <t>106148428.565511</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>86.578</t>
+          <t>86578303.5980781</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>94.674</t>
+          <t>94673592.398973</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>107.666</t>
+          <t>107666044.991537</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>115.059</t>
+          <t>115059443.422831</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>131.174</t>
+          <t>131174336.867741</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>140.079</t>
+          <t>140079236.538629</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>154.711</t>
+          <t>154711088.166391</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>121.111</t>
+          <t>121111422.034465</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>122.485</t>
+          <t>122484568.891022</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>119.834</t>
+          <t>119834274.094701</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>130.898</t>
+          <t>130898053.891018</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>146.007</t>
+          <t>146007453.163818</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>126.67</t>
+          <t>126669768.739609</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>11975.96</t>
+          <t>11975959557.8171</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11606.789</t>
+          <t>11606788958.2671</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>8206.472</t>
+          <t>8206471724.72693</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>10224.91</t>
+          <t>10224909599.755</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>11107.955</t>
+          <t>11107955256.3538</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>10696.403</t>
+          <t>10696402998.7799</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12038.016</t>
+          <t>12038015959.4413</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>13431.588</t>
+          <t>13431588484.4431</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>13172.052</t>
+          <t>13172051634.5099</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>12833.442</t>
+          <t>12833441799.2683</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>12424.649</t>
+          <t>12424648741.6836</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>12635.416</t>
+          <t>12635415699.8479</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>12848.714</t>
+          <t>12848713762.2144</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>13558.943</t>
+          <t>13558943054.8387</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>12868.262</t>
+          <t>12868261576.9999</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>8302.471</t>
+          <t>8302470972.98739</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8756.19</t>
+          <t>8756190384.21142</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8980.636</t>
+          <t>8980636347.95976</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>9322.448</t>
+          <t>9322448369.27185</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>8856.906</t>
+          <t>8856905780.68341</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8619.64</t>
+          <t>8619640120.95712</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7269.152</t>
+          <t>7269152416.74904</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6772.718</t>
+          <t>6772717593.06031</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6525.7</t>
+          <t>6525699886.90537</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>6291.131</t>
+          <t>6291130908.47213</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>6693.326</t>
+          <t>6693325715.41717</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6818.15</t>
+          <t>6818149711.31017</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>7147.104</t>
+          <t>7147104361.46222</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>7739.008</t>
+          <t>7739008058.51935</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>6915.834</t>
+          <t>6915833686.21508</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>3446.449</t>
+          <t>3446449259.9316</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3501.074</t>
+          <t>3501073845.83105</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3030.531</t>
+          <t>3030530974.60418</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3381.477</t>
+          <t>3381476839.64092</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>3430.407</t>
+          <t>3430406825.488</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>3556.962</t>
+          <t>3556961821.82497</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3747.414</t>
+          <t>3747414023.62683</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3748.434</t>
+          <t>3748433728.29072</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3795.017</t>
+          <t>3795016869.34546</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>3823.821</t>
+          <t>3823820651.47681</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3781.319</t>
+          <t>3781319462.21474</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3614.812</t>
+          <t>3614811754.18923</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>3621.003</t>
+          <t>3621002547.07144</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>3738.756</t>
+          <t>3738756275.24002</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>3117.643</t>
+          <t>3117642678.42045</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4556.109</t>
+          <t>4556109175.92402</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4544.977</t>
+          <t>4544976928.14483</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3742.185</t>
+          <t>3742184679.86802</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4493.324</t>
+          <t>4493323867.47433</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>5216.98</t>
+          <t>5216980039.46819</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6012.619</t>
+          <t>6012619095.03139</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6343.908</t>
+          <t>6343908039.27565</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5013.093</t>
+          <t>5013092976.17347</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4986.8</t>
+          <t>4986800376.81408</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>4453.149</t>
+          <t>4453149444.8987</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>4901.182</t>
+          <t>4901182323.01639</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>4802.552</t>
+          <t>4802552397.45272</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>5100.749</t>
+          <t>5100748843.03275</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>5535.76</t>
+          <t>5535759738.03007</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>5000.694</t>
+          <t>5000693681.47438</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>56931.836</t>
+          <t>56931835800.5542</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>59226.26</t>
+          <t>59226259544.9034</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>53649.128</t>
+          <t>53649128029.5567</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>48547.707</t>
+          <t>48547706693.9645</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>45287.527</t>
+          <t>45287526592.8526</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>50888.842</t>
+          <t>50888842469.0544</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>49817.636</t>
+          <t>49817635817.2805</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>51411.157</t>
+          <t>51411156856.3713</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>55835.887</t>
+          <t>55835887103.628</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>58723.866</t>
+          <t>58723865880.6122</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>61724.372</t>
+          <t>61724371914.0202</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>61727.963</t>
+          <t>61727963485.5591</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>68904.51</t>
+          <t>68904509574.1213</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>73795.621</t>
+          <t>73795621235.7778</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>72594.946</t>
+          <t>72594945623.797</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>689.46</t>
+          <t>689460295.079033</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>741.415</t>
+          <t>741415013.210763</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>707.335</t>
+          <t>707335268.068798</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>701.189</t>
+          <t>701188618.658284</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>636.36</t>
+          <t>636359713.949663</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>638.991</t>
+          <t>638990591.430382</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>650.585</t>
+          <t>650584787.360696</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>644.289</t>
+          <t>644288985.172631</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>724.855</t>
+          <t>724855455.491623</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>878.729</t>
+          <t>878729138.045269</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>896.437</t>
+          <t>896437343.060408</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>963.457</t>
+          <t>963457316.311592</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>1169.084</t>
+          <t>1169084145.52168</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>1146.199</t>
+          <t>1146198894.38499</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>1305.383</t>
+          <t>1305383385.8634</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>875.253</t>
+          <t>875253027.706719</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>836.314</t>
+          <t>836314310.703078</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>725.046</t>
+          <t>725046210.893024</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>764.913</t>
+          <t>764912631.256004</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>776.477</t>
+          <t>776476704.479687</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>783.674</t>
+          <t>783674059.512995</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>816.132</t>
+          <t>816131958.217734</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>832.315</t>
+          <t>832314999.381313</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>928.574</t>
+          <t>928573555.682655</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>883.883</t>
+          <t>883883034.804586</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>853.106</t>
+          <t>853106188.600937</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>858.451</t>
+          <t>858451270.359489</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>862.77</t>
+          <t>862769794.187009</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1199.451</t>
+          <t>1199450868.75471</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1148.724</t>
+          <t>1148724221.28487</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>4836.145</t>
+          <t>4836144559.92482</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4955.592</t>
+          <t>4955591791.62743</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4248.214</t>
+          <t>4248213845.2179</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4634.039</t>
+          <t>4634038696.99874</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4766.689</t>
+          <t>4766688908.04856</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5239.529</t>
+          <t>5239529193.85792</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5334.795</t>
+          <t>5334794952.2191</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>5490.902</t>
+          <t>5490901651.99126</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5875.842</t>
+          <t>5875842153.3868</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>6080.401</t>
+          <t>6080401165.56075</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>6258.896</t>
+          <t>6258896447.5244</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6307.547</t>
+          <t>6307546524.51819</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>6691.737</t>
+          <t>6691736578.09713</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>6035.202</t>
+          <t>6035202453.60704</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>5130.118</t>
+          <t>5130118192.59193</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7558.891</t>
+          <t>7558890668.99779</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>8667.815</t>
+          <t>8667815115.61164</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9079.881</t>
+          <t>9079880872.31008</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>8923.76</t>
+          <t>8923760032.68709</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>9530.251</t>
+          <t>9530251082.1654</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8569.109</t>
+          <t>8569109419.62556</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>7760.494</t>
+          <t>7760493556.03897</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>7029.191</t>
+          <t>7029191053.3679</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>7329.968</t>
+          <t>7329968444.982</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>7869.734</t>
+          <t>7869734106.88682</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>7829.612</t>
+          <t>7829611673.11892</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>7508.452</t>
+          <t>7508451956.30076</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>7519.044</t>
+          <t>7519044490.19457</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>13076.689</t>
+          <t>13076689019.8669</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>11502.362</t>
+          <t>11502362239.6737</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>9113.996</t>
+          <t>9113995785.50573</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9657.874</t>
+          <t>9657874385.65693</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>8775.3</t>
+          <t>8775299622.09746</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>8397.601</t>
+          <t>8397601046.59968</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8296.314</t>
+          <t>8296313588.49171</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8910.149</t>
+          <t>8910149130.50167</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8659.551</t>
+          <t>8659550796.17721</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>8541.101</t>
+          <t>8541101148.25489</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8711.03</t>
+          <t>8711029839.86232</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8912.351</t>
+          <t>8912351190.90533</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>8985.529</t>
+          <t>8985528665.73859</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>8845.457</t>
+          <t>8845456883.36856</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>8100.793</t>
+          <t>8100793255.18308</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>8202.819</t>
+          <t>8202818547.43782</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>7193.987</t>
+          <t>7193986561.1959</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>127117.342</t>
+          <t>127117342051.982</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>126819.462</t>
+          <t>126819461643.896</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>130495.878</t>
+          <t>130495878469.801</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>140827.921</t>
+          <t>140827921151.404</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>148007.369</t>
+          <t>148007368996.208</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>166667.124</t>
+          <t>166667123582.821</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>171727.13</t>
+          <t>171727130493.177</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>174676.567</t>
+          <t>174676566927.432</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>179798.995</t>
+          <t>179798995052.287</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>185318.581</t>
+          <t>185318580946.895</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>189054.025</t>
+          <t>189054024606.396</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>187923.467</t>
+          <t>187923467333.517</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>176109.673</t>
+          <t>176109673439.396</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>164200.05</t>
+          <t>164200049940.332</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>153642.359</t>
+          <t>153642358680.157</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>742448.71</t>
+          <t>742448709676.181</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>740936.338</t>
+          <t>740936337803.628</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>767960.538</t>
+          <t>767960537869.977</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>775860.238</t>
+          <t>775860238354.776</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>801483.282</t>
+          <t>801483281542.723</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>851036.789</t>
+          <t>851036789374.323</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>874236.658</t>
+          <t>874236657980.234</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>883623.229</t>
+          <t>883623228716.019</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>895601.324</t>
+          <t>895601324303.045</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>890900.963</t>
+          <t>890900963153.679</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>924148.135</t>
+          <t>924148135234.101</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>955103.176</t>
+          <t>955103176174.291</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>923173.991</t>
+          <t>923173991277.514</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>943236.368</t>
+          <t>943236367883.127</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>940203.039</t>
+          <t>940203038568.453</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2227044.637</t>
+          <t>2227044637178.93</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2188495.868</t>
+          <t>2188495867943.95</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2191485.132</t>
+          <t>2191485132308.58</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2196377.781</t>
+          <t>2196377781252.34</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2215966.832</t>
+          <t>2215966831720.79</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2290890.413</t>
+          <t>2290890413456.44</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2330012.83</t>
+          <t>2330012829688.5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2333605.768</t>
+          <t>2333605767677.49</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2394691.084</t>
+          <t>2394691083645.35</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2423868.866</t>
+          <t>2423868865592.26</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2464422.182</t>
+          <t>2464422182369.79</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2489620.335</t>
+          <t>2489620335373.55</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2399825.543</t>
+          <t>2399825543450.04</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2416116.012</t>
+          <t>2416116012024.99</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2390424.026</t>
+          <t>2390424026398.89</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>labour_force_value.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA1</t>
